--- a/hydrological_data/smhi_api_stasjoner.xlsx
+++ b/hydrological_data/smhi_api_stasjoner.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Prosjekter\2022_oppdatering_av_hydark\svensk_tilsig_fra_SMHI\smhi_api\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\NAS\Prosjekter\Oppdatering_av_hydark\Sverige\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCE3164-4054-4EB4-A264-9851FD151B75}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB22859B-ADAD-43C0-9D6D-C4672B5647C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
-  <si>
-    <t>Stasjonsnr</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Navn_SMHI</t>
   </si>
@@ -39,9 +36,6 @@
     <t>9801-E</t>
   </si>
   <si>
-    <t>Franshammar</t>
-  </si>
-  <si>
     <t>9802-E</t>
   </si>
   <si>
@@ -75,12 +69,6 @@
     <t>9810-E</t>
   </si>
   <si>
-    <t>Granaaker</t>
-  </si>
-  <si>
-    <t>9811-E</t>
-  </si>
-  <si>
     <t>Gimdalsby</t>
   </si>
   <si>
@@ -102,7 +90,24 @@
     <t>9808-E</t>
   </si>
   <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Stasjonsnr_SMHI</t>
+  </si>
+  <si>
     <t>Seriekode_EMPS</t>
+  </si>
+  <si>
+    <t>Bruker Nissafors 2 til den legges ned 2021-05-11 og deretter bruke 2606-Hestraviken</t>
+  </si>
+  <si>
+    <t>9802-E er serie 1159-Rolfstad for perioden 1980-1981, deretter 2273-Hassela.
+Rolfstad er skalert basert på en enkel linær regresjon av overlappende data med Hassela for perioden 1981-2021 slik at estimert vannføring brukt til serie 9802-E basert på Rolfstad blir:
+Q= 0.50418492452496*Q_Rolfstad-0.710350948815963. (Brukt for årene 1980-1981).</t>
   </si>
 </sst>
 </file>
@@ -138,9 +143,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,169 +432,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" customWidth="1"/>
+    <col min="3" max="3" width="22.90625" customWidth="1"/>
+    <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>654</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>1159</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>2273</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>591</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>2238</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>1328</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>2153</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>97</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>1901</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>654</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>948</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1159</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2273</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>591</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>2238</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>1328</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2153</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>2237</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>2606</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>97</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>1083</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>1901</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>2606</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>1083</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D10:D11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>